--- a/public/downloads/ads-report-template.xlsx
+++ b/public/downloads/ads-report-template.xlsx
@@ -1616,7 +1616,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Need help reading your numbers? Request a free audit: https://www.magnuspath.com/free-ecommerce-audit/</t>
+          <t>Need help reading your numbers? Request a free audit: https://www.billionecommerceagency.com/free-ecommerce-audit/</t>
         </is>
       </c>
     </row>
